--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4681,31 +4681,28 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.004682466352329423</v>
+        <v>13</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -4715,7 +4712,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -4725,12 +4722,12 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -4738,47 +4735,47 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4807,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4840,33 +4837,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>SRC_BR_SINAN</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -4896,7 +4893,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>country:BR:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4916,7 +4913,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -4931,12 +4928,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>BR_SINAN_MENI_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -4949,7 +4946,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -4959,12 +4956,12 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -4972,45 +4969,438 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.004682466352329423</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV24" t="inlineStr">
+      <c r="AV25" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="BA24" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr">
+      <c r="BB25" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>10</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -5132,7 +5522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -5142,7 +5532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -5162,7 +5552,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -5194,7 +5584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15563</v>
+        <v>15578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1597</v>
+        <v>2623</v>
       </c>
       <c r="O21" t="n">
-        <v>1597</v>
+        <v>2623</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7477898764670088</v>
+        <v>1.228210924216008</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1597</v>
+        <v>2623</v>
       </c>
       <c r="O22" t="n">
-        <v>1597</v>
+        <v>2623</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5080,13 +5080,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>2173</v>
       </c>
       <c r="O25" t="n">
-        <v>10</v>
+        <v>2173</v>
       </c>
       <c r="R25" t="n">
-        <v>0.004682466352329423</v>
+        <v>1.017499938361184</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>2173</v>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>2173</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -5401,6 +5401,399 @@
         </is>
       </c>
       <c r="BC26" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>357</v>
+      </c>
+      <c r="O27" t="n">
+        <v>357</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1671640487781604</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>357</v>
+      </c>
+      <c r="O28" t="n">
+        <v>357</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -5439,7 +5832,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5915,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -5532,7 +5925,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -5552,7 +5945,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -5584,7 +5977,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15578</v>
+        <v>19124</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -4557,6 +4557,11 @@
       <c r="O30" t="n">
         <v>7</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4569,13 +4574,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -8481,6 +8496,11 @@
       <c r="O59" t="n">
         <v>5</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8493,13 +8513,23 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -12405,6 +12435,11 @@
       <c r="O88" t="n">
         <v>9</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12417,13 +12452,23 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -16326,6 +16371,11 @@
       <c r="O117" t="n">
         <v>8</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16338,13 +16388,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -20247,6 +20307,11 @@
       <c r="O146" t="n">
         <v>11</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20259,13 +20324,23 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -24168,6 +24243,11 @@
       <c r="O175" t="n">
         <v>23</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24180,13 +24260,23 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
       </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV175" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -28089,6 +28179,11 @@
       <c r="O204" t="n">
         <v>15</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28101,13 +28196,23 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -32010,6 +32115,11 @@
       <c r="O233" t="n">
         <v>20</v>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32022,12 +32132,22 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
         <v>0</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
